--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.97.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.97.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.97.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.97.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="50" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.97.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.97.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0097.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0097.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -598,11 +598,15 @@
       <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L6: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: the Masterâ€™</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]shall be inse</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]shall be inse</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L13: isolated marker/symbol line :: ;</t>
@@ -641,7 +645,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -653,7 +657,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L32: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -704,7 +708,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L34: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: The Masterâ€™s Office.</t>
+          <t>L94: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: ••</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -716,7 +720,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L32: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -743,7 +747,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -753,11 +757,7 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: form of the decree :â€”</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -804,11 +804,7 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢â€¢</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr"/>
@@ -898,7 +894,11 @@
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr"/>
-      <c r="O8" s="1" t="inlineStr"/>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t>L94: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: ••</t>
+        </is>
+      </c>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
       <c r="R8" s="1" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
